--- a/docs/경기장.xlsx
+++ b/docs/경기장.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="26">
   <si>
     <t>벽</t>
   </si>
@@ -34,7 +34,7 @@
     <t>│11-1</t>
   </si>
   <si>
-    <t>로봇은 7, 8, 9, 10, 11, 12,START에서만 회전이 가능 (라인트레이싱은 선 위에서라면 아무때나 가능)</t>
+    <t>START와 │,├,─,┼ 외에는 검은 선이 없음!</t>
   </si>
   <si>
     <t>│10-2</t>
@@ -43,7 +43,7 @@
     <t>│11-2</t>
   </si>
   <si>
-    <t>9번노드에서 10번노드로 이동 방법 : 9-3 -&gt; 10-2</t>
+    <t>로봇은 7, 8, 9, 10, 11, 12,START에서만 회전이 가능 (라인트레이싱은 선 위에서라면 아무때나 가능)</t>
   </si>
   <si>
     <t>├7</t>
@@ -70,6 +70,9 @@
     <t>│11-3</t>
   </si>
   <si>
+    <t>9번노드에서 10번노드로 이동 방법 : 9-3 -&gt; 10-2</t>
+  </si>
+  <si>
     <t>10번노드에서 11번 노드로 이동 방법 : 10-2 -&gt; 11-2</t>
   </si>
   <si>
@@ -79,10 +82,10 @@
     <t>10번노드에서 9번 노드로 이동 방법 : 10-2 -&gt; 9-2</t>
   </si>
   <si>
-    <t>START노드에서 9번 노드로 이동 방법 : START -&gt; 12 -&gt; 9-2</t>
+    <t>START</t>
   </si>
   <si>
-    <t>START</t>
+    <t>START노드에서 9번 노드로 이동 방법 : START -&gt; 12 -&gt; 9-2</t>
   </si>
   <si>
     <t>9번노드에서 START노드로 이동 방법 : 9-3 -&gt; 10-2 -&gt; 11-2 -&gt;START</t>
@@ -356,6 +359,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
@@ -855,6 +859,9 @@
         <v>0</v>
       </c>
       <c r="M11" s="2"/>
+      <c r="N11" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
@@ -28561,6 +28568,9 @@
       <c r="Z1000" s="2"/>
     </row>
   </sheetData>
+  <printOptions gridLines="1" horizontalCentered="1"/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/경기장.xlsx
+++ b/docs/경기장.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="27">
   <si>
     <t>벽</t>
   </si>
@@ -34,7 +34,10 @@
     <t>│11-1</t>
   </si>
   <si>
-    <t>START와 │,├,─,┼ 외에는 검은 선이 없음!</t>
+    <t>START와 │,├,─,┼ 외에는 검은 선이 없음! (노드 사이의 ...도 아무것도 없는 빈 땅)</t>
+  </si>
+  <si>
+    <t>...</t>
   </si>
   <si>
     <t>│10-2</t>
@@ -579,20 +582,24 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="1" t="s">
+      <c r="H5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="K5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
@@ -612,37 +619,37 @@
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="1"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="5"/>
       <c r="K6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>0</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
@@ -669,18 +676,22 @@
         <v>4</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="F7" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
+      <c r="K7" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="L7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -711,18 +722,22 @@
       <c r="E8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
+      <c r="K8" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="L8" s="4" t="s">
         <v>0</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -750,17 +765,21 @@
         <v>0</v>
       </c>
       <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
+      <c r="K9" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="L9" s="4" t="s">
         <v>0</v>
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
@@ -793,20 +812,22 @@
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="H10" s="5"/>
       <c r="I10" s="5">
         <v>12.0</v>
       </c>
-      <c r="J10" s="4"/>
+      <c r="J10" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>0</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
@@ -860,7 +881,7 @@
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>

--- a/docs/경기장.xlsx
+++ b/docs/경기장.xlsx
@@ -581,7 +581,9 @@
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="4"/>
+      <c r="G5" s="5">
+        <v>13.0</v>
+      </c>
       <c r="H5" s="5" t="s">
         <v>8</v>
       </c>

--- a/docs/경기장.xlsx
+++ b/docs/경기장.xlsx
@@ -21,22 +21,10 @@
     <x:t>11번노드에서 START노드로 이동 방법 : 11-3 에서 160도 방향 바라보고 이동 -&gt; START</x:t>
   </x:si>
   <x:si>
-    <x:t>10번노드에서 START노드로 이동 방법 : 10-3 -&gt; 13 -&gt; START</x:t>
-  </x:si>
-  <x:si>
-    <x:t>┼8</x:t>
+    <x:t>벽</x:t>
   </x:si>
   <x:si>
     <x:t>│</x:t>
-  </x:si>
-  <x:si>
-    <x:t>벽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>─</x:t>
   </x:si>
   <x:si>
     <x:t>├7</x:t>
@@ -45,10 +33,52 @@
     <x:t>...</x:t>
   </x:si>
   <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>┼8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>─</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11번노드에서 10번 노드로 이동 방법 : 11-2 -&gt; 10-2</x:t>
+  </x:si>
+  <x:si>
     <x:t>10번노드에서 11번 노드로 이동 방법 : 10-2 -&gt; 11-2</x:t>
   </x:si>
   <x:si>
-    <x:t>11번노드에서 10번 노드로 이동 방법 : 11-2 -&gt; 10-2</x:t>
+    <x:t>│11-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>START</x:t>
+  </x:si>
+  <x:si>
+    <x:t>│10-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>│10-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>─9-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>│10-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>│11-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>─9-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>─9-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>│11-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10번노드에서 START노드로 이동 방법 : 10-3 -&gt; 13 -&gt; START</x:t>
   </x:si>
   <x:si>
     <x:t>검은 선은 │,├,─,┼ 이 있는 곳에 모양에 맞게 그려짐</x:t>
@@ -57,7 +87,16 @@
     <x:t>9번노드에서 10번노드로 이동 방법 : 9-3 -&gt; 10-2</x:t>
   </x:si>
   <x:si>
+    <x:t>로봇은 7, 8, 9, 10, 11, 13,12,START에서만 회전이 가능 (라인트레이싱은 선 위에서라면 아무때나 가능)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>START글씨를 검은 선이 네모로 감싸고 있음</x:t>
+  </x:si>
+  <x:si>
     <x:t>START노드에서 9번 노드로 이동 방법 : START -&gt; 13 -&gt; 9-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9번노드에서 START노드로 이동 방법 : 9-3 -&gt; 13 -&gt; START</x:t>
   </x:si>
   <x:si>
     <x:t>10번노드에서 9번 노드로 이동 방법 : 10-2 -&gt; 12 -&gt; 9-2</x:t>
@@ -66,46 +105,7 @@
     <x:t>11번 노드에서 9번 노드로 이동 방법 : 11-2 -&gt; 12 -&gt; 9-2</x:t>
   </x:si>
   <x:si>
-    <x:t>9번노드에서 START노드로 이동 방법 : 9-3 -&gt; 13 -&gt; START</x:t>
-  </x:si>
-  <x:si>
-    <x:t>START글씨를 검은 선이 네모로 감싸고 있음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로봇은 7, 8, 9, 10, 11, 13,12,START에서만 회전이 가능 (라인트레이싱은 선 위에서라면 아무때나 가능)</x:t>
-  </x:si>
-  <x:si>
     <x:t>START와 │,├,─,┼ 외에는 검은 선이 없음!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>│11-3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>─9-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>START</x:t>
-  </x:si>
-  <x:si>
-    <x:t>│10-3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>│10-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>│10-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>│11-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>│11-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>─9-3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>─9-2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -313,7 +313,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -396,7 +395,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -431,7 +429,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -476,7 +473,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -520,7 +516,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -605,7 +600,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -626,7 +620,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -657,7 +650,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -922,40 +914,40 @@
   <x:sheetData>
     <x:row r="1" spans="1:26" ht="13.75">
       <x:c r="A1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N1" s="2" t="s">
         <x:v>6</x:v>
@@ -974,39 +966,39 @@
     </x:row>
     <x:row r="2" spans="1:26" ht="13.75">
       <x:c r="A2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F2" s="1"/>
       <x:c r="G2" s="4"/>
       <x:c r="H2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K2" s="1">
         <x:v>6</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N2" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="O2" s="3"/>
       <x:c r="P2" s="3"/>
@@ -1022,35 +1014,35 @@
     </x:row>
     <x:row r="3" spans="1:26" ht="13.75">
       <x:c r="A3" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B3" s="6" t="s">
-        <x:v>9</x:v>
+      <x:c r="C3" s="1" t="s">
+        <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="D3" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D3" s="6" t="s">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F3" s="1"/>
       <x:c r="G3" s="4"/>
       <x:c r="H3" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I3" s="6"/>
       <x:c r="J3" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K3" s="6"/>
       <x:c r="L3" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N3" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="O3" s="3"/>
       <x:c r="P3" s="3"/>
@@ -1066,39 +1058,39 @@
     </x:row>
     <x:row r="4" spans="1:26" ht="13.75">
       <x:c r="A4" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1"/>
       <x:c r="H4" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L4" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N4" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O4" s="3"/>
       <x:c r="P4" s="3"/>
@@ -1114,31 +1106,31 @@
     </x:row>
     <x:row r="5" spans="1:26" ht="13.75">
       <x:c r="A5" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E5" s="1"/>
       <x:c r="F5" s="6"/>
       <x:c r="G5" s="6"/>
       <x:c r="H5" s="6"/>
       <x:c r="I5" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J5" s="6"/>
       <x:c r="K5" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="L5" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N5" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="U5" s="3"/>
       <x:c r="V5" s="3"/>
@@ -1149,39 +1141,39 @@
     </x:row>
     <x:row r="6" spans="1:26" ht="13.75">
       <x:c r="A6" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G6" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H6" s="6"/>
       <x:c r="I6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J6" s="6"/>
       <x:c r="K6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L6" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N6" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O6" s="3"/>
       <x:c r="P6" s="3"/>
@@ -1197,14 +1189,14 @@
     </x:row>
     <x:row r="7" spans="1:26" ht="13.75">
       <x:c r="A7" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C7" s="1"/>
       <x:c r="D7" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F7" s="6"/>
       <x:c r="H7" s="2"/>
@@ -1212,7 +1204,7 @@
       <x:c r="J7" s="2"/>
       <x:c r="K7" s="6"/>
       <x:c r="L7" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N7" s="7" t="s">
         <x:v>0</x:v>
@@ -1231,28 +1223,28 @@
     </x:row>
     <x:row r="8" spans="1:26" ht="13.75">
       <x:c r="A8" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
-      <x:c r="G8" s="6"/>
-      <x:c r="I8" s="6">
+      <x:c r="G8">
         <x:v>12</x:v>
       </x:c>
+      <x:c r="I8" s="6"/>
       <x:c r="J8" s="4"/>
       <x:c r="K8" s="6"/>
       <x:c r="L8" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N8" s="5" t="s">
         <x:v>10</x:v>
@@ -1271,29 +1263,29 @@
     </x:row>
     <x:row r="9" spans="1:26" ht="13.75">
       <x:c r="A9" s="4" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>9</x:v>
+      <x:c r="C9" s="4" t="s">
+        <x:v>2</x:v>
       </x:c>
-      <x:c r="C9" s="4" t="s">
+      <x:c r="D9" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="s">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H9" s="2"/>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="6"/>
       <x:c r="L9" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N9" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="O9" s="3"/>
       <x:c r="P9" s="3"/>
@@ -1309,34 +1301,35 @@
     </x:row>
     <x:row r="10" spans="1:26" ht="13.75">
       <x:c r="A10" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="4">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D10" s="4">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F10" s="4"/>
       <x:c r="G10" s="4"/>
-      <x:c r="I10" s="6">
+      <x:c r="H10">
         <x:v>13</x:v>
       </x:c>
+      <x:c r="I10" s="6"/>
       <x:c r="J10" s="6"/>
       <x:c r="K10" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L10" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N10" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="O10" s="3"/>
       <x:c r="P10" s="3"/>
@@ -1352,43 +1345,43 @@
     </x:row>
     <x:row r="11" spans="1:26" ht="13.75">
       <x:c r="A11" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F11" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G11" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H11" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I11" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J11" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N11" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="O11" s="3"/>
       <x:c r="P11" s="3"/>
@@ -1417,7 +1410,7 @@
       <x:c r="L12" s="3"/>
       <x:c r="M12" s="3"/>
       <x:c r="N12" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O12" s="3"/>
       <x:c r="P12" s="3"/>
@@ -1446,7 +1439,7 @@
       <x:c r="L13" s="3"/>
       <x:c r="M13" s="3"/>
       <x:c r="N13" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="O13" s="3"/>
       <x:c r="P13" s="3"/>
@@ -1476,7 +1469,7 @@
       <x:c r="L14" s="3"/>
       <x:c r="M14" s="3"/>
       <x:c r="N14" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="O14" s="3"/>
       <x:c r="P14" s="3"/>
